--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0002T0006Z000C1N15_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0002T0006Z000C1N15_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>36.1617851733545</v>
+        <v>5.876290090670107</v>
       </c>
       <c r="D2" t="n">
-        <v>36.15412803387702</v>
+        <v>5.875045805505017</v>
       </c>
       <c r="E2" t="n">
-        <v>9.496755380205263</v>
+        <v>1.543222749283355</v>
       </c>
       <c r="F2" t="n">
-        <v>9.560550233421319</v>
+        <v>1.553589412930965</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>35.73848262702616</v>
+        <v>5.807503426891751</v>
       </c>
       <c r="D3" t="n">
-        <v>35.77870766285655</v>
+        <v>5.81403999521419</v>
       </c>
       <c r="E3" t="n">
-        <v>9.496755380205263</v>
+        <v>1.543222749283355</v>
       </c>
       <c r="F3" t="n">
-        <v>9.560550233421319</v>
+        <v>1.553589412930965</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.17180763220771</v>
+        <v>5.877918740233753</v>
       </c>
       <c r="D4" t="n">
-        <v>35.94955943192357</v>
+        <v>5.84180340768758</v>
       </c>
       <c r="E4" t="n">
-        <v>9.496755380205263</v>
+        <v>1.543222749283355</v>
       </c>
       <c r="F4" t="n">
-        <v>9.560550233421319</v>
+        <v>1.553589412930965</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>40.11361170530208</v>
+        <v>6.518461902111589</v>
       </c>
       <c r="D5" t="n">
-        <v>39.89461535641148</v>
+        <v>6.482874995416865</v>
       </c>
       <c r="E5" t="n">
-        <v>9.496755380205263</v>
+        <v>1.543222749283355</v>
       </c>
       <c r="F5" t="n">
-        <v>9.560550233421319</v>
+        <v>1.553589412930965</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>38.46658478150286</v>
+        <v>6.250820026994215</v>
       </c>
       <c r="D6" t="n">
-        <v>38.26920098203234</v>
+        <v>6.218745159580256</v>
       </c>
       <c r="E6" t="n">
-        <v>9.496755380205263</v>
+        <v>1.543222749283355</v>
       </c>
       <c r="F6" t="n">
-        <v>9.560550233421319</v>
+        <v>1.553589412930965</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>24.65478470326133</v>
+        <v>4.006402514279967</v>
       </c>
       <c r="D7" t="n">
-        <v>24.86235805339114</v>
+        <v>4.040133183676061</v>
       </c>
       <c r="E7" t="n">
-        <v>9.496755380205263</v>
+        <v>1.543222749283355</v>
       </c>
       <c r="F7" t="n">
-        <v>9.560550233421319</v>
+        <v>1.553589412930965</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>18.48557487354318</v>
+        <v>3.003905916950766</v>
       </c>
       <c r="D8" t="n">
-        <v>18.70322578091952</v>
+        <v>3.039274189399422</v>
       </c>
       <c r="E8" t="n">
-        <v>9.496755380205263</v>
+        <v>1.543222749283355</v>
       </c>
       <c r="F8" t="n">
-        <v>9.560550233421319</v>
+        <v>1.553589412930965</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>9.353383687554276</v>
+        <v>1.51992484922757</v>
       </c>
       <c r="D9" t="n">
-        <v>9.5474258054379</v>
+        <v>1.551456693383659</v>
       </c>
       <c r="E9" t="n">
-        <v>9.496755380205263</v>
+        <v>1.543222749283355</v>
       </c>
       <c r="F9" t="n">
-        <v>9.560550233421319</v>
+        <v>1.553589412930965</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>17.00191503063187</v>
+        <v>2.76281119247768</v>
       </c>
       <c r="D10" t="n">
-        <v>16.96864385799413</v>
+        <v>2.757404626924046</v>
       </c>
       <c r="E10" t="n">
-        <v>9.496755380205263</v>
+        <v>1.543222749283355</v>
       </c>
       <c r="F10" t="n">
-        <v>9.560550233421319</v>
+        <v>1.553589412930965</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>35.8503835404867</v>
+        <v>5.825687325329089</v>
       </c>
       <c r="D11" t="n">
-        <v>38.45771648252688</v>
+        <v>6.249378928410619</v>
       </c>
       <c r="E11" t="n">
-        <v>9.496755380205263</v>
+        <v>1.543222749283355</v>
       </c>
       <c r="F11" t="n">
-        <v>9.560550233421319</v>
+        <v>1.553589412930965</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>33.09432884663345</v>
+        <v>5.377828437577935</v>
       </c>
       <c r="D12" t="n">
-        <v>33.0912307814628</v>
+        <v>5.377325001987705</v>
       </c>
       <c r="E12" t="n">
-        <v>9.496755380205263</v>
+        <v>1.543222749283355</v>
       </c>
       <c r="F12" t="n">
-        <v>9.560550233421319</v>
+        <v>1.553589412930965</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>30.74671998547604</v>
+        <v>4.996341997639856</v>
       </c>
       <c r="D13" t="n">
-        <v>30.91750685407777</v>
+        <v>5.024094863787638</v>
       </c>
       <c r="E13" t="n">
-        <v>9.496755380205263</v>
+        <v>1.543222749283355</v>
       </c>
       <c r="F13" t="n">
-        <v>9.560550233421319</v>
+        <v>1.553589412930965</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
